--- a/data/trans_dic/IQ2601_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ2601_R2-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>68,72%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>45,67%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>64,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,68; 76,33</t>
+          <t>56,33; 73,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,12; 54,16</t>
+          <t>30,95; 49,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,54; 75,69</t>
+          <t>52,0; 71,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,01; 97,08</t>
+          <t>44,28; 85,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,99; 73,77</t>
+          <t>59,7; 76,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,63; 48,05</t>
+          <t>36,62; 53,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 71,98</t>
+          <t>54,51; 75,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,21; 86,72</t>
+          <t>49,03; 95,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,11; 72,49</t>
+          <t>60,32; 72,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,06; 49,23</t>
+          <t>36,45; 49,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,4; 70,3</t>
+          <t>55,74; 70,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,74; 88,67</t>
+          <t>54,51; 87,11</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>72,23%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>65,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>50,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>64,97%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>66,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>49,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,04; 69,45</t>
+          <t>59,67; 66,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,46; 54,44</t>
+          <t>45,42; 53,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,45; 68,77</t>
+          <t>61,34; 68,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,36; 74,46</t>
+          <t>64,59; 78,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,48; 66,37</t>
+          <t>61,76; 69,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,29; 52,75</t>
+          <t>46,06; 54,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,33; 68,4</t>
+          <t>61,38; 68,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,26; 79,67</t>
+          <t>56,86; 74,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,71; 67,04</t>
+          <t>61,87; 66,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,9; 52,54</t>
+          <t>46,75; 52,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62,37; 67,59</t>
+          <t>62,6; 67,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,47; 75,28</t>
+          <t>64,09; 74,57</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71,84%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53,54%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77,91%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>72,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>62,62%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,94%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,81; 78,24</t>
+          <t>65,7; 77,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,37; 68,56</t>
+          <t>47,65; 60,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,58; 67,13</t>
+          <t>57,05; 68,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,01; 81,85</t>
+          <t>63,41; 88,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,84; 77,54</t>
+          <t>66,6; 78,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,0; 59,83</t>
+          <t>56,04; 68,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,84; 68,65</t>
+          <t>55,61; 68,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,24; 87,15</t>
+          <t>58,91; 81,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,36; 76,27</t>
+          <t>68,39; 76,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,06; 62,32</t>
+          <t>53,51; 62,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,81; 66,46</t>
+          <t>58,08; 66,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,2; 81,72</t>
+          <t>65,05; 81,38</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,02; 70,61</t>
+          <t>62,3; 68,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,05; 55,47</t>
+          <t>46,03; 52,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,16; 66,79</t>
+          <t>61,19; 67,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,91; 75,68</t>
+          <t>67,04; 78,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,58; 68,27</t>
+          <t>65,16; 70,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,14; 52,36</t>
+          <t>49,44; 55,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,56; 67,25</t>
+          <t>60,93; 66,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,0; 79,36</t>
+          <t>61,36; 74,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,51; 68,47</t>
+          <t>64,27; 68,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,5; 53,16</t>
+          <t>48,5; 53,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,99; 66,26</t>
+          <t>62,25; 66,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,07; 75,65</t>
+          <t>66,6; 75,37</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>54983</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42743</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8548</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>61106</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>41159</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>38076</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54983</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33925</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42743</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>14730</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53963; 67873</t>
+          <t>47465; 61811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32547; 48811</t>
+          <t>26480; 42373</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32072; 44510</t>
+          <t>35676; 48997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5956; 10322</t>
+          <t>5488; 10654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48025; 62166</t>
+          <t>53091; 68190</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26212; 41116</t>
+          <t>32998; 48594</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35864; 49386</t>
+          <t>32055; 44185</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5699; 11992</t>
+          <t>3767; 7326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105829; 125545</t>
+          <t>104471; 125124</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65101; 86481</t>
+          <t>64029; 86673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71863; 89580</t>
+          <t>71026; 90421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14125; 21690</t>
+          <t>10944; 17489</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>296470</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>234781</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>316906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88764</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>266875</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>219987</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>302667</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58860</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>296470</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>234781</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>316906</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96605</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>145913</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>252123; 282234</t>
+          <t>279690; 312998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>203527; 238450</t>
+          <t>216418; 252716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>286292; 320377</t>
+          <t>298409; 334070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51456; 65658</t>
+          <t>79372; 97011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>278816; 311097</t>
+          <t>251006; 282137</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>215798; 251308</t>
+          <t>201770; 237767</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>298379; 332748</t>
+          <t>285959; 318643</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86936; 106138</t>
+          <t>49592; 64574</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>540098; 586744</t>
+          <t>541436; 584544</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>428864; 480461</t>
+          <t>427570; 478803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>593962; 643728</t>
+          <t>596223; 641990</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142723; 166667</t>
+          <t>134665; 156681</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110294</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87507</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114699</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>123054</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>99962</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>103523</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31035</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>110294</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87507</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>114699</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>64540</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113123; 132485</t>
+          <t>100861; 118347</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89977; 109434</t>
+          <t>77878; 98227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92164; 113350</t>
+          <t>103953; 124932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25522; 35399</t>
+          <t>27319; 37932</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101084; 119049</t>
+          <t>112775; 132375</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76812; 97788</t>
+          <t>89452; 109824</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>103575; 125097</t>
+          <t>93897; 115061</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28279; 38976</t>
+          <t>25716; 35564</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>220714; 246241</t>
+          <t>220781; 245555</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>171422; 201330</t>
+          <t>172874; 202005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202956; 233327</t>
+          <t>203916; 234431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57359; 71892</t>
+          <t>56425; 70589</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>461747</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>461747</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>432164; 469291</t>
+          <t>440182; 482109</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>337344; 381526</t>
+          <t>333900; 380035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>424179; 463217</t>
+          <t>451187; 497019</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89370; 107503</t>
+          <t>119578; 140854</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>442131; 482357</t>
+          <t>433101; 470992</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>334736; 379823</t>
+          <t>340065; 382882</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>453926; 495865</t>
+          <t>422565; 463696</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128483; 152196</t>
+          <t>85022; 103047</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>884503; 938823</t>
+          <t>881314; 936123</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>685372; 751256</t>
+          <t>685404; 750463</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>887063; 948036</t>
+          <t>890646; 946107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>223897; 252531</t>
+          <t>211054; 238878</t>
         </is>
       </c>
     </row>
